--- a/vitalcore-expo/automation/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/vitalcore-expo/automation/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="1036">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="1044">
   <si>
     <t>Test ID</t>
   </si>
@@ -82,6 +82,12 @@
     <t>Authentication scenario verification #9</t>
   </si>
   <si>
+    <t>TC_AUTH_010</t>
+  </si>
+  <si>
+    <t>Authentication scenario verification #10</t>
+  </si>
+  <si>
     <t>TC_AUTH_011</t>
   </si>
   <si>
@@ -1042,6 +1048,12 @@
     <t>Forms scenario verification #7</t>
   </si>
   <si>
+    <t>TC_FORM_008</t>
+  </si>
+  <si>
+    <t>Forms scenario verification #8</t>
+  </si>
+  <si>
     <t>TC_FORM_009</t>
   </si>
   <si>
@@ -2233,6 +2245,12 @@
     <t>Notifications scenario verification #3</t>
   </si>
   <si>
+    <t>TC_NOTIF_004</t>
+  </si>
+  <si>
+    <t>Notifications scenario verification #4</t>
+  </si>
+  <si>
     <t>TC_NOTIF_005</t>
   </si>
   <si>
@@ -2336,6 +2354,12 @@
   </si>
   <si>
     <t>File Upload scenario verification #1</t>
+  </si>
+  <si>
+    <t>TC_UPLD_002</t>
+  </si>
+  <si>
+    <t>File Upload scenario verification #2</t>
   </si>
   <si>
     <t>TC_UPLD_003</t>
@@ -3495,7 +3519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D507"/>
+  <dimension ref="A1:D511"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3529,7 +3553,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>0.32</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -3543,7 +3567,7 @@
         <v>8</v>
       </c>
       <c r="D3">
-        <v>0.95</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -3557,7 +3581,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -3571,7 +3595,7 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -3585,7 +3609,7 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -3613,7 +3637,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -3627,7 +3651,7 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -3641,7 +3665,7 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>0.8</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -3655,7 +3679,7 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>0.99</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -3669,7 +3693,7 @@
         <v>26</v>
       </c>
       <c r="D12">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -3683,7 +3707,7 @@
         <v>28</v>
       </c>
       <c r="D13">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -3697,7 +3721,7 @@
         <v>30</v>
       </c>
       <c r="D14">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -3711,7 +3735,7 @@
         <v>32</v>
       </c>
       <c r="D15">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -3725,7 +3749,7 @@
         <v>34</v>
       </c>
       <c r="D16">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -3739,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="D17">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3753,7 +3777,7 @@
         <v>38</v>
       </c>
       <c r="D18">
-        <v>0.97</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -3767,7 +3791,7 @@
         <v>40</v>
       </c>
       <c r="D19">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -3781,7 +3805,7 @@
         <v>42</v>
       </c>
       <c r="D20">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -3795,7 +3819,7 @@
         <v>44</v>
       </c>
       <c r="D21">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -3809,7 +3833,7 @@
         <v>46</v>
       </c>
       <c r="D22">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -3823,7 +3847,7 @@
         <v>48</v>
       </c>
       <c r="D23">
-        <v>0.8</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -3837,7 +3861,7 @@
         <v>50</v>
       </c>
       <c r="D24">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -3851,7 +3875,7 @@
         <v>52</v>
       </c>
       <c r="D25">
-        <v>0.23</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -3865,7 +3889,7 @@
         <v>54</v>
       </c>
       <c r="D26">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -3879,7 +3903,7 @@
         <v>56</v>
       </c>
       <c r="D27">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -3893,7 +3917,7 @@
         <v>58</v>
       </c>
       <c r="D28">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -3907,7 +3931,7 @@
         <v>60</v>
       </c>
       <c r="D29">
-        <v>0.77</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -3921,7 +3945,7 @@
         <v>62</v>
       </c>
       <c r="D30">
-        <v>0.55</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -3935,7 +3959,7 @@
         <v>64</v>
       </c>
       <c r="D31">
-        <v>0.94</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -3949,7 +3973,7 @@
         <v>66</v>
       </c>
       <c r="D32">
-        <v>0.87</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -3963,7 +3987,7 @@
         <v>68</v>
       </c>
       <c r="D33">
-        <v>0.65</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -3977,7 +4001,7 @@
         <v>70</v>
       </c>
       <c r="D34">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -3991,7 +4015,7 @@
         <v>72</v>
       </c>
       <c r="D35">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -4005,7 +4029,7 @@
         <v>74</v>
       </c>
       <c r="D36">
-        <v>0.56</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -4019,7 +4043,7 @@
         <v>76</v>
       </c>
       <c r="D37">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -4033,7 +4057,7 @@
         <v>78</v>
       </c>
       <c r="D38">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -4047,7 +4071,7 @@
         <v>80</v>
       </c>
       <c r="D39">
-        <v>0.64</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -4061,7 +4085,7 @@
         <v>82</v>
       </c>
       <c r="D40">
-        <v>0.62</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -4069,27 +4093,27 @@
         <v>83</v>
       </c>
       <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s">
         <v>84</v>
       </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
       <c r="D41">
-        <v>0.78</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" t="s">
         <v>86</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
       </c>
       <c r="C42" t="s">
         <v>87</v>
       </c>
       <c r="D42">
-        <v>0.74</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -4097,13 +4121,13 @@
         <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
         <v>89</v>
       </c>
       <c r="D43">
-        <v>0.76</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -4111,13 +4135,13 @@
         <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C44" t="s">
         <v>91</v>
       </c>
       <c r="D44">
-        <v>0.72</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -4125,13 +4149,13 @@
         <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
         <v>93</v>
       </c>
       <c r="D45">
-        <v>0.83</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -4139,13 +4163,13 @@
         <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
         <v>95</v>
       </c>
       <c r="D46">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -4153,13 +4177,13 @@
         <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
         <v>97</v>
       </c>
       <c r="D47">
-        <v>0.99</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -4167,13 +4191,13 @@
         <v>98</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C48" t="s">
         <v>99</v>
       </c>
       <c r="D48">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -4181,13 +4205,13 @@
         <v>100</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C49" t="s">
         <v>101</v>
       </c>
       <c r="D49">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -4195,13 +4219,13 @@
         <v>102</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
         <v>103</v>
       </c>
       <c r="D50">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -4209,13 +4233,13 @@
         <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C51" t="s">
         <v>105</v>
       </c>
       <c r="D51">
-        <v>0.93</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -4223,13 +4247,13 @@
         <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C52" t="s">
         <v>107</v>
       </c>
       <c r="D52">
-        <v>0.9</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -4237,13 +4261,13 @@
         <v>108</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C53" t="s">
         <v>109</v>
       </c>
       <c r="D53">
-        <v>0.74</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -4251,13 +4275,13 @@
         <v>110</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
         <v>111</v>
       </c>
       <c r="D54">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -4265,13 +4289,13 @@
         <v>112</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C55" t="s">
         <v>113</v>
       </c>
       <c r="D55">
-        <v>0.86</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -4279,13 +4303,13 @@
         <v>114</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C56" t="s">
         <v>115</v>
       </c>
       <c r="D56">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -4293,13 +4317,13 @@
         <v>116</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C57" t="s">
         <v>117</v>
       </c>
       <c r="D57">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -4307,13 +4331,13 @@
         <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C58" t="s">
         <v>119</v>
       </c>
       <c r="D58">
-        <v>0.78</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -4321,13 +4345,13 @@
         <v>120</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C59" t="s">
         <v>121</v>
       </c>
       <c r="D59">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -4335,13 +4359,13 @@
         <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
         <v>123</v>
       </c>
       <c r="D60">
-        <v>0.78</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -4349,13 +4373,13 @@
         <v>124</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C61" t="s">
         <v>125</v>
       </c>
       <c r="D61">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -4363,13 +4387,13 @@
         <v>126</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C62" t="s">
         <v>127</v>
       </c>
       <c r="D62">
-        <v>0.31</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -4377,13 +4401,13 @@
         <v>128</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
         <v>129</v>
       </c>
       <c r="D63">
-        <v>0.24</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -4391,13 +4415,13 @@
         <v>130</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
         <v>131</v>
       </c>
       <c r="D64">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -4405,13 +4429,13 @@
         <v>132</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
         <v>133</v>
       </c>
       <c r="D65">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -4419,13 +4443,13 @@
         <v>134</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
         <v>135</v>
       </c>
       <c r="D66">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -4433,13 +4457,13 @@
         <v>136</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C67" t="s">
         <v>137</v>
       </c>
       <c r="D67">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -4447,13 +4471,13 @@
         <v>138</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
         <v>139</v>
       </c>
       <c r="D68">
-        <v>0.58</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -4461,13 +4485,13 @@
         <v>140</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C69" t="s">
         <v>141</v>
       </c>
       <c r="D69">
-        <v>0.29</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -4475,13 +4499,13 @@
         <v>142</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C70" t="s">
         <v>143</v>
       </c>
       <c r="D70">
-        <v>0.72</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -4489,27 +4513,27 @@
         <v>144</v>
       </c>
       <c r="B71" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" t="s">
         <v>145</v>
       </c>
-      <c r="C71" t="s">
-        <v>146</v>
-      </c>
       <c r="D71">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>146</v>
+      </c>
+      <c r="B72" t="s">
         <v>147</v>
-      </c>
-      <c r="B72" t="s">
-        <v>145</v>
       </c>
       <c r="C72" t="s">
         <v>148</v>
       </c>
       <c r="D72">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -4517,13 +4541,13 @@
         <v>149</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C73" t="s">
         <v>150</v>
       </c>
       <c r="D73">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -4531,13 +4555,13 @@
         <v>151</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C74" t="s">
         <v>152</v>
       </c>
       <c r="D74">
-        <v>0.99</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -4545,13 +4569,13 @@
         <v>153</v>
       </c>
       <c r="B75" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C75" t="s">
         <v>154</v>
       </c>
       <c r="D75">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -4559,13 +4583,13 @@
         <v>155</v>
       </c>
       <c r="B76" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C76" t="s">
         <v>156</v>
       </c>
       <c r="D76">
-        <v>0.98</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -4573,13 +4597,13 @@
         <v>157</v>
       </c>
       <c r="B77" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C77" t="s">
         <v>158</v>
       </c>
       <c r="D77">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -4587,13 +4611,13 @@
         <v>159</v>
       </c>
       <c r="B78" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C78" t="s">
         <v>160</v>
       </c>
       <c r="D78">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -4601,13 +4625,13 @@
         <v>161</v>
       </c>
       <c r="B79" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C79" t="s">
         <v>162</v>
       </c>
       <c r="D79">
-        <v>0.54</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -4615,13 +4639,13 @@
         <v>163</v>
       </c>
       <c r="B80" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C80" t="s">
         <v>164</v>
       </c>
       <c r="D80">
-        <v>0.84</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -4629,13 +4653,13 @@
         <v>165</v>
       </c>
       <c r="B81" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C81" t="s">
         <v>166</v>
       </c>
       <c r="D81">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -4643,13 +4667,13 @@
         <v>167</v>
       </c>
       <c r="B82" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C82" t="s">
         <v>168</v>
       </c>
       <c r="D82">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -4657,13 +4681,13 @@
         <v>169</v>
       </c>
       <c r="B83" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C83" t="s">
         <v>170</v>
       </c>
       <c r="D83">
-        <v>0.83</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -4671,13 +4695,13 @@
         <v>171</v>
       </c>
       <c r="B84" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C84" t="s">
         <v>172</v>
       </c>
       <c r="D84">
-        <v>0.82</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -4685,13 +4709,13 @@
         <v>173</v>
       </c>
       <c r="B85" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C85" t="s">
         <v>174</v>
       </c>
       <c r="D85">
-        <v>0.97</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -4699,13 +4723,13 @@
         <v>175</v>
       </c>
       <c r="B86" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C86" t="s">
         <v>176</v>
       </c>
       <c r="D86">
-        <v>0.86</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -4713,13 +4737,13 @@
         <v>177</v>
       </c>
       <c r="B87" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C87" t="s">
         <v>178</v>
       </c>
       <c r="D87">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -4727,13 +4751,13 @@
         <v>179</v>
       </c>
       <c r="B88" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C88" t="s">
         <v>180</v>
       </c>
       <c r="D88">
-        <v>0.49</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -4741,13 +4765,13 @@
         <v>181</v>
       </c>
       <c r="B89" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C89" t="s">
         <v>182</v>
       </c>
       <c r="D89">
-        <v>0.8</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -4755,13 +4779,13 @@
         <v>183</v>
       </c>
       <c r="B90" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C90" t="s">
         <v>184</v>
       </c>
       <c r="D90">
-        <v>0.28</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -4769,27 +4793,27 @@
         <v>185</v>
       </c>
       <c r="B91" t="s">
+        <v>147</v>
+      </c>
+      <c r="C91" t="s">
         <v>186</v>
       </c>
-      <c r="C91" t="s">
-        <v>187</v>
-      </c>
       <c r="D91">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>187</v>
+      </c>
+      <c r="B92" t="s">
         <v>188</v>
-      </c>
-      <c r="B92" t="s">
-        <v>186</v>
       </c>
       <c r="C92" t="s">
         <v>189</v>
       </c>
       <c r="D92">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -4797,13 +4821,13 @@
         <v>190</v>
       </c>
       <c r="B93" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C93" t="s">
         <v>191</v>
       </c>
       <c r="D93">
-        <v>0.88</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -4811,13 +4835,13 @@
         <v>192</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C94" t="s">
         <v>193</v>
       </c>
       <c r="D94">
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -4825,13 +4849,13 @@
         <v>194</v>
       </c>
       <c r="B95" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C95" t="s">
         <v>195</v>
       </c>
       <c r="D95">
-        <v>0.99</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -4839,13 +4863,13 @@
         <v>196</v>
       </c>
       <c r="B96" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C96" t="s">
         <v>197</v>
       </c>
       <c r="D96">
-        <v>0.96</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -4853,13 +4877,13 @@
         <v>198</v>
       </c>
       <c r="B97" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C97" t="s">
         <v>199</v>
       </c>
       <c r="D97">
-        <v>0.86</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -4867,13 +4891,13 @@
         <v>200</v>
       </c>
       <c r="B98" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C98" t="s">
         <v>201</v>
       </c>
       <c r="D98">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -4881,13 +4905,13 @@
         <v>202</v>
       </c>
       <c r="B99" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C99" t="s">
         <v>203</v>
       </c>
       <c r="D99">
-        <v>0.79</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -4895,13 +4919,13 @@
         <v>204</v>
       </c>
       <c r="B100" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C100" t="s">
         <v>205</v>
       </c>
       <c r="D100">
-        <v>0.92</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -4909,13 +4933,13 @@
         <v>206</v>
       </c>
       <c r="B101" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C101" t="s">
         <v>207</v>
       </c>
       <c r="D101">
-        <v>0.95</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -4923,13 +4947,13 @@
         <v>208</v>
       </c>
       <c r="B102" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C102" t="s">
         <v>209</v>
       </c>
       <c r="D102">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -4937,13 +4961,13 @@
         <v>210</v>
       </c>
       <c r="B103" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C103" t="s">
         <v>211</v>
       </c>
       <c r="D103">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -4951,13 +4975,13 @@
         <v>212</v>
       </c>
       <c r="B104" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C104" t="s">
         <v>213</v>
       </c>
       <c r="D104">
-        <v>0.22</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -4965,13 +4989,13 @@
         <v>214</v>
       </c>
       <c r="B105" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C105" t="s">
         <v>215</v>
       </c>
       <c r="D105">
-        <v>0.92</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -4979,13 +5003,13 @@
         <v>216</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C106" t="s">
         <v>217</v>
       </c>
       <c r="D106">
-        <v>0.62</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -4993,13 +5017,13 @@
         <v>218</v>
       </c>
       <c r="B107" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C107" t="s">
         <v>219</v>
       </c>
       <c r="D107">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -5007,13 +5031,13 @@
         <v>220</v>
       </c>
       <c r="B108" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C108" t="s">
         <v>221</v>
       </c>
       <c r="D108">
-        <v>0.88</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -5021,13 +5045,13 @@
         <v>222</v>
       </c>
       <c r="B109" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C109" t="s">
         <v>223</v>
       </c>
       <c r="D109">
-        <v>0.88</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -5035,13 +5059,13 @@
         <v>224</v>
       </c>
       <c r="B110" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C110" t="s">
         <v>225</v>
       </c>
       <c r="D110">
-        <v>0.67</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -5049,27 +5073,27 @@
         <v>226</v>
       </c>
       <c r="B111" t="s">
+        <v>188</v>
+      </c>
+      <c r="C111" t="s">
         <v>227</v>
       </c>
-      <c r="C111" t="s">
-        <v>228</v>
-      </c>
       <c r="D111">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>228</v>
+      </c>
+      <c r="B112" t="s">
         <v>229</v>
-      </c>
-      <c r="B112" t="s">
-        <v>227</v>
       </c>
       <c r="C112" t="s">
         <v>230</v>
       </c>
       <c r="D112">
-        <v>0.39</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
@@ -5077,13 +5101,13 @@
         <v>231</v>
       </c>
       <c r="B113" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C113" t="s">
         <v>232</v>
       </c>
       <c r="D113">
-        <v>0.87</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
@@ -5091,13 +5115,13 @@
         <v>233</v>
       </c>
       <c r="B114" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C114" t="s">
         <v>234</v>
       </c>
       <c r="D114">
-        <v>0.94</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
@@ -5105,13 +5129,13 @@
         <v>235</v>
       </c>
       <c r="B115" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C115" t="s">
         <v>236</v>
       </c>
       <c r="D115">
-        <v>0.79</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
@@ -5119,13 +5143,13 @@
         <v>237</v>
       </c>
       <c r="B116" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C116" t="s">
         <v>238</v>
       </c>
       <c r="D116">
-        <v>0.87</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
@@ -5133,13 +5157,13 @@
         <v>239</v>
       </c>
       <c r="B117" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C117" t="s">
         <v>240</v>
       </c>
       <c r="D117">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
@@ -5147,13 +5171,13 @@
         <v>241</v>
       </c>
       <c r="B118" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C118" t="s">
         <v>242</v>
       </c>
       <c r="D118">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
@@ -5161,13 +5185,13 @@
         <v>243</v>
       </c>
       <c r="B119" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C119" t="s">
         <v>244</v>
       </c>
       <c r="D119">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -5175,13 +5199,13 @@
         <v>245</v>
       </c>
       <c r="B120" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C120" t="s">
         <v>246</v>
       </c>
       <c r="D120">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
@@ -5189,13 +5213,13 @@
         <v>247</v>
       </c>
       <c r="B121" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C121" t="s">
         <v>248</v>
       </c>
       <c r="D121">
-        <v>0.99</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
@@ -5203,13 +5227,13 @@
         <v>249</v>
       </c>
       <c r="B122" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C122" t="s">
         <v>250</v>
       </c>
       <c r="D122">
-        <v>0.94</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -5217,13 +5241,13 @@
         <v>251</v>
       </c>
       <c r="B123" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C123" t="s">
         <v>252</v>
       </c>
       <c r="D123">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
@@ -5231,13 +5255,13 @@
         <v>253</v>
       </c>
       <c r="B124" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C124" t="s">
         <v>254</v>
       </c>
       <c r="D124">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
@@ -5245,13 +5269,13 @@
         <v>255</v>
       </c>
       <c r="B125" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C125" t="s">
         <v>256</v>
       </c>
       <c r="D125">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
@@ -5259,13 +5283,13 @@
         <v>257</v>
       </c>
       <c r="B126" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C126" t="s">
         <v>258</v>
       </c>
       <c r="D126">
-        <v>0.56</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
@@ -5273,13 +5297,13 @@
         <v>259</v>
       </c>
       <c r="B127" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C127" t="s">
         <v>260</v>
       </c>
       <c r="D127">
-        <v>0.89</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
@@ -5287,13 +5311,13 @@
         <v>261</v>
       </c>
       <c r="B128" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C128" t="s">
         <v>262</v>
       </c>
       <c r="D128">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -5301,13 +5325,13 @@
         <v>263</v>
       </c>
       <c r="B129" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C129" t="s">
         <v>264</v>
       </c>
       <c r="D129">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
@@ -5315,13 +5339,13 @@
         <v>265</v>
       </c>
       <c r="B130" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C130" t="s">
         <v>266</v>
       </c>
       <c r="D130">
-        <v>0.74</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
@@ -5329,13 +5353,13 @@
         <v>267</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C131" t="s">
         <v>268</v>
       </c>
       <c r="D131">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
@@ -5343,13 +5367,13 @@
         <v>269</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C132" t="s">
         <v>270</v>
       </c>
       <c r="D132">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
@@ -5357,13 +5381,13 @@
         <v>271</v>
       </c>
       <c r="B133" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C133" t="s">
         <v>272</v>
       </c>
       <c r="D133">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
@@ -5371,13 +5395,13 @@
         <v>273</v>
       </c>
       <c r="B134" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C134" t="s">
         <v>274</v>
       </c>
       <c r="D134">
-        <v>0.98</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -5385,13 +5409,13 @@
         <v>275</v>
       </c>
       <c r="B135" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C135" t="s">
         <v>276</v>
       </c>
       <c r="D135">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
@@ -5399,13 +5423,13 @@
         <v>277</v>
       </c>
       <c r="B136" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C136" t="s">
         <v>278</v>
       </c>
       <c r="D136">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
@@ -5413,13 +5437,13 @@
         <v>279</v>
       </c>
       <c r="B137" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C137" t="s">
         <v>280</v>
       </c>
       <c r="D137">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
@@ -5427,13 +5451,13 @@
         <v>281</v>
       </c>
       <c r="B138" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C138" t="s">
         <v>282</v>
       </c>
       <c r="D138">
-        <v>0.68</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
@@ -5441,7 +5465,7 @@
         <v>283</v>
       </c>
       <c r="B139" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C139" t="s">
         <v>284</v>
@@ -5455,13 +5479,13 @@
         <v>285</v>
       </c>
       <c r="B140" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C140" t="s">
         <v>286</v>
       </c>
       <c r="D140">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
@@ -5469,27 +5493,27 @@
         <v>287</v>
       </c>
       <c r="B141" t="s">
+        <v>229</v>
+      </c>
+      <c r="C141" t="s">
         <v>288</v>
       </c>
-      <c r="C141" t="s">
-        <v>289</v>
-      </c>
       <c r="D141">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>289</v>
+      </c>
+      <c r="B142" t="s">
         <v>290</v>
-      </c>
-      <c r="B142" t="s">
-        <v>288</v>
       </c>
       <c r="C142" t="s">
         <v>291</v>
       </c>
       <c r="D142">
-        <v>0.92</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
@@ -5497,13 +5521,13 @@
         <v>292</v>
       </c>
       <c r="B143" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C143" t="s">
         <v>293</v>
       </c>
       <c r="D143">
-        <v>0.87</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
@@ -5511,13 +5535,13 @@
         <v>294</v>
       </c>
       <c r="B144" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C144" t="s">
         <v>295</v>
       </c>
       <c r="D144">
-        <v>0.9</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
@@ -5525,13 +5549,13 @@
         <v>296</v>
       </c>
       <c r="B145" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C145" t="s">
         <v>297</v>
       </c>
       <c r="D145">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
@@ -5539,13 +5563,13 @@
         <v>298</v>
       </c>
       <c r="B146" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C146" t="s">
         <v>299</v>
       </c>
       <c r="D146">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
@@ -5553,7 +5577,7 @@
         <v>300</v>
       </c>
       <c r="B147" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C147" t="s">
         <v>301</v>
@@ -5567,13 +5591,13 @@
         <v>302</v>
       </c>
       <c r="B148" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C148" t="s">
         <v>303</v>
       </c>
       <c r="D148">
-        <v>0.78</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
@@ -5581,13 +5605,13 @@
         <v>304</v>
       </c>
       <c r="B149" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C149" t="s">
         <v>305</v>
       </c>
       <c r="D149">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
@@ -5595,13 +5619,13 @@
         <v>306</v>
       </c>
       <c r="B150" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C150" t="s">
         <v>307</v>
       </c>
       <c r="D150">
-        <v>0.93</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
@@ -5609,13 +5633,13 @@
         <v>308</v>
       </c>
       <c r="B151" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C151" t="s">
         <v>309</v>
       </c>
       <c r="D151">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
@@ -5623,13 +5647,13 @@
         <v>310</v>
       </c>
       <c r="B152" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C152" t="s">
         <v>311</v>
       </c>
       <c r="D152">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
@@ -5637,13 +5661,13 @@
         <v>312</v>
       </c>
       <c r="B153" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C153" t="s">
         <v>313</v>
       </c>
       <c r="D153">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
@@ -5651,13 +5675,13 @@
         <v>314</v>
       </c>
       <c r="B154" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C154" t="s">
         <v>315</v>
       </c>
       <c r="D154">
-        <v>0.87</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
@@ -5665,13 +5689,13 @@
         <v>316</v>
       </c>
       <c r="B155" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C155" t="s">
         <v>317</v>
       </c>
       <c r="D155">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
@@ -5679,13 +5703,13 @@
         <v>318</v>
       </c>
       <c r="B156" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C156" t="s">
         <v>319</v>
       </c>
       <c r="D156">
-        <v>0.99</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
@@ -5693,13 +5717,13 @@
         <v>320</v>
       </c>
       <c r="B157" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C157" t="s">
         <v>321</v>
       </c>
       <c r="D157">
-        <v>0.8</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
@@ -5707,13 +5731,13 @@
         <v>322</v>
       </c>
       <c r="B158" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C158" t="s">
         <v>323</v>
       </c>
       <c r="D158">
-        <v>0.88</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
@@ -5721,13 +5745,13 @@
         <v>324</v>
       </c>
       <c r="B159" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C159" t="s">
         <v>325</v>
       </c>
       <c r="D159">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
@@ -5735,13 +5759,13 @@
         <v>326</v>
       </c>
       <c r="B160" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C160" t="s">
         <v>327</v>
       </c>
       <c r="D160">
-        <v>0.87</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
@@ -5749,27 +5773,27 @@
         <v>328</v>
       </c>
       <c r="B161" t="s">
+        <v>290</v>
+      </c>
+      <c r="C161" t="s">
         <v>329</v>
       </c>
-      <c r="C161" t="s">
-        <v>330</v>
-      </c>
       <c r="D161">
-        <v>0.77</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>330</v>
+      </c>
+      <c r="B162" t="s">
         <v>331</v>
-      </c>
-      <c r="B162" t="s">
-        <v>329</v>
       </c>
       <c r="C162" t="s">
         <v>332</v>
       </c>
       <c r="D162">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
@@ -5777,13 +5801,13 @@
         <v>333</v>
       </c>
       <c r="B163" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C163" t="s">
         <v>334</v>
       </c>
       <c r="D163">
-        <v>0.25</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
@@ -5791,13 +5815,13 @@
         <v>335</v>
       </c>
       <c r="B164" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C164" t="s">
         <v>336</v>
       </c>
       <c r="D164">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
@@ -5805,13 +5829,13 @@
         <v>337</v>
       </c>
       <c r="B165" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C165" t="s">
         <v>338</v>
       </c>
       <c r="D165">
-        <v>0.77</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
@@ -5819,13 +5843,13 @@
         <v>339</v>
       </c>
       <c r="B166" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C166" t="s">
         <v>340</v>
       </c>
       <c r="D166">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
@@ -5833,13 +5857,13 @@
         <v>341</v>
       </c>
       <c r="B167" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C167" t="s">
         <v>342</v>
       </c>
       <c r="D167">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
@@ -5847,13 +5871,13 @@
         <v>343</v>
       </c>
       <c r="B168" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C168" t="s">
         <v>344</v>
       </c>
       <c r="D168">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
@@ -5861,13 +5885,13 @@
         <v>345</v>
       </c>
       <c r="B169" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C169" t="s">
         <v>346</v>
       </c>
       <c r="D169">
-        <v>0.54</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
@@ -5875,13 +5899,13 @@
         <v>347</v>
       </c>
       <c r="B170" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C170" t="s">
         <v>348</v>
       </c>
       <c r="D170">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
@@ -5889,13 +5913,13 @@
         <v>349</v>
       </c>
       <c r="B171" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C171" t="s">
         <v>350</v>
       </c>
       <c r="D171">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
@@ -5903,13 +5927,13 @@
         <v>351</v>
       </c>
       <c r="B172" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C172" t="s">
         <v>352</v>
       </c>
       <c r="D172">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
@@ -5917,13 +5941,13 @@
         <v>353</v>
       </c>
       <c r="B173" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C173" t="s">
         <v>354</v>
       </c>
       <c r="D173">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
@@ -5931,13 +5955,13 @@
         <v>355</v>
       </c>
       <c r="B174" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C174" t="s">
         <v>356</v>
       </c>
       <c r="D174">
-        <v>0.9</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
@@ -5945,13 +5969,13 @@
         <v>357</v>
       </c>
       <c r="B175" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C175" t="s">
         <v>358</v>
       </c>
       <c r="D175">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
@@ -5959,13 +5983,13 @@
         <v>359</v>
       </c>
       <c r="B176" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C176" t="s">
         <v>360</v>
       </c>
       <c r="D176">
-        <v>0.98</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
@@ -5973,13 +5997,13 @@
         <v>361</v>
       </c>
       <c r="B177" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C177" t="s">
         <v>362</v>
       </c>
       <c r="D177">
-        <v>0.92</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
@@ -5987,13 +6011,13 @@
         <v>363</v>
       </c>
       <c r="B178" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C178" t="s">
         <v>364</v>
       </c>
       <c r="D178">
-        <v>0.74</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
@@ -6001,13 +6025,13 @@
         <v>365</v>
       </c>
       <c r="B179" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C179" t="s">
         <v>366</v>
       </c>
       <c r="D179">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
@@ -6015,13 +6039,13 @@
         <v>367</v>
       </c>
       <c r="B180" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C180" t="s">
         <v>368</v>
       </c>
       <c r="D180">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
@@ -6029,13 +6053,13 @@
         <v>369</v>
       </c>
       <c r="B181" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C181" t="s">
         <v>370</v>
       </c>
       <c r="D181">
-        <v>0.68</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
@@ -6043,13 +6067,13 @@
         <v>371</v>
       </c>
       <c r="B182" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C182" t="s">
         <v>372</v>
       </c>
       <c r="D182">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
@@ -6057,13 +6081,13 @@
         <v>373</v>
       </c>
       <c r="B183" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C183" t="s">
         <v>374</v>
       </c>
       <c r="D183">
-        <v>0.45</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
@@ -6071,13 +6095,13 @@
         <v>375</v>
       </c>
       <c r="B184" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C184" t="s">
         <v>376</v>
       </c>
       <c r="D184">
-        <v>0.71</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
@@ -6085,13 +6109,13 @@
         <v>377</v>
       </c>
       <c r="B185" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C185" t="s">
         <v>378</v>
       </c>
       <c r="D185">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
@@ -6099,13 +6123,13 @@
         <v>379</v>
       </c>
       <c r="B186" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C186" t="s">
         <v>380</v>
       </c>
       <c r="D186">
-        <v>0.87</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
@@ -6113,13 +6137,13 @@
         <v>381</v>
       </c>
       <c r="B187" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C187" t="s">
         <v>382</v>
       </c>
       <c r="D187">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
@@ -6127,13 +6151,13 @@
         <v>383</v>
       </c>
       <c r="B188" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C188" t="s">
         <v>384</v>
       </c>
       <c r="D188">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
@@ -6141,13 +6165,13 @@
         <v>385</v>
       </c>
       <c r="B189" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C189" t="s">
         <v>386</v>
       </c>
       <c r="D189">
-        <v>0.96</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
@@ -6155,13 +6179,13 @@
         <v>387</v>
       </c>
       <c r="B190" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C190" t="s">
         <v>388</v>
       </c>
       <c r="D190">
-        <v>0.91</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
@@ -6169,13 +6193,13 @@
         <v>389</v>
       </c>
       <c r="B191" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C191" t="s">
         <v>390</v>
       </c>
       <c r="D191">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
@@ -6183,13 +6207,13 @@
         <v>391</v>
       </c>
       <c r="B192" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C192" t="s">
         <v>392</v>
       </c>
       <c r="D192">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
@@ -6197,13 +6221,13 @@
         <v>393</v>
       </c>
       <c r="B193" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C193" t="s">
         <v>394</v>
       </c>
       <c r="D193">
-        <v>0.72</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
@@ -6211,13 +6235,13 @@
         <v>395</v>
       </c>
       <c r="B194" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C194" t="s">
         <v>396</v>
       </c>
       <c r="D194">
-        <v>0.79</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
@@ -6225,13 +6249,13 @@
         <v>397</v>
       </c>
       <c r="B195" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C195" t="s">
         <v>398</v>
       </c>
       <c r="D195">
-        <v>0.86</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
@@ -6239,13 +6263,13 @@
         <v>399</v>
       </c>
       <c r="B196" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C196" t="s">
         <v>400</v>
       </c>
       <c r="D196">
-        <v>0.86</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
@@ -6253,13 +6277,13 @@
         <v>401</v>
       </c>
       <c r="B197" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C197" t="s">
         <v>402</v>
       </c>
       <c r="D197">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
@@ -6267,13 +6291,13 @@
         <v>403</v>
       </c>
       <c r="B198" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C198" t="s">
         <v>404</v>
       </c>
       <c r="D198">
-        <v>0.59</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
@@ -6281,13 +6305,13 @@
         <v>405</v>
       </c>
       <c r="B199" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C199" t="s">
         <v>406</v>
       </c>
       <c r="D199">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
@@ -6295,41 +6319,41 @@
         <v>407</v>
       </c>
       <c r="B200" t="s">
+        <v>331</v>
+      </c>
+      <c r="C200" t="s">
         <v>408</v>
       </c>
-      <c r="C200" t="s">
-        <v>409</v>
-      </c>
       <c r="D200">
-        <v>0.83</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>409</v>
+      </c>
+      <c r="B201" t="s">
+        <v>331</v>
+      </c>
+      <c r="C201" t="s">
         <v>410</v>
       </c>
-      <c r="B201" t="s">
-        <v>408</v>
-      </c>
-      <c r="C201" t="s">
-        <v>411</v>
-      </c>
       <c r="D201">
-        <v>0.93</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>411</v>
+      </c>
+      <c r="B202" t="s">
         <v>412</v>
-      </c>
-      <c r="B202" t="s">
-        <v>408</v>
       </c>
       <c r="C202" t="s">
         <v>413</v>
       </c>
       <c r="D202">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
@@ -6337,13 +6361,13 @@
         <v>414</v>
       </c>
       <c r="B203" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C203" t="s">
         <v>415</v>
       </c>
       <c r="D203">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
@@ -6351,13 +6375,13 @@
         <v>416</v>
       </c>
       <c r="B204" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C204" t="s">
         <v>417</v>
       </c>
       <c r="D204">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
@@ -6365,13 +6389,13 @@
         <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C205" t="s">
         <v>419</v>
       </c>
       <c r="D205">
-        <v>0.75</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
@@ -6379,13 +6403,13 @@
         <v>420</v>
       </c>
       <c r="B206" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C206" t="s">
         <v>421</v>
       </c>
       <c r="D206">
-        <v>0.78</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
@@ -6393,13 +6417,13 @@
         <v>422</v>
       </c>
       <c r="B207" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C207" t="s">
         <v>423</v>
       </c>
       <c r="D207">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
@@ -6407,13 +6431,13 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C208" t="s">
         <v>425</v>
       </c>
       <c r="D208">
-        <v>0.41</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
@@ -6421,13 +6445,13 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C209" t="s">
         <v>427</v>
       </c>
       <c r="D209">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
@@ -6435,13 +6459,13 @@
         <v>428</v>
       </c>
       <c r="B210" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C210" t="s">
         <v>429</v>
       </c>
       <c r="D210">
-        <v>0.76</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
@@ -6449,13 +6473,13 @@
         <v>430</v>
       </c>
       <c r="B211" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C211" t="s">
         <v>431</v>
       </c>
       <c r="D211">
-        <v>0.83</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
@@ -6463,13 +6487,13 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C212" t="s">
         <v>433</v>
       </c>
       <c r="D212">
-        <v>0.29</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
@@ -6477,13 +6501,13 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C213" t="s">
         <v>435</v>
       </c>
       <c r="D213">
-        <v>0.7</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
@@ -6491,13 +6515,13 @@
         <v>436</v>
       </c>
       <c r="B214" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C214" t="s">
         <v>437</v>
       </c>
       <c r="D214">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
@@ -6505,13 +6529,13 @@
         <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C215" t="s">
         <v>439</v>
       </c>
       <c r="D215">
-        <v>0.87</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
@@ -6519,13 +6543,13 @@
         <v>440</v>
       </c>
       <c r="B216" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C216" t="s">
         <v>441</v>
       </c>
       <c r="D216">
-        <v>0.9</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
@@ -6533,13 +6557,13 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C217" t="s">
         <v>443</v>
       </c>
       <c r="D217">
-        <v>0.83</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
@@ -6547,13 +6571,13 @@
         <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C218" t="s">
         <v>445</v>
       </c>
       <c r="D218">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
@@ -6561,13 +6585,13 @@
         <v>446</v>
       </c>
       <c r="B219" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C219" t="s">
         <v>447</v>
       </c>
       <c r="D219">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
@@ -6575,13 +6599,13 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C220" t="s">
         <v>449</v>
       </c>
       <c r="D220">
-        <v>0.76</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
@@ -6589,13 +6613,13 @@
         <v>450</v>
       </c>
       <c r="B221" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C221" t="s">
         <v>451</v>
       </c>
       <c r="D221">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
@@ -6603,13 +6627,13 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C222" t="s">
         <v>453</v>
       </c>
       <c r="D222">
-        <v>0.75</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
@@ -6617,13 +6641,13 @@
         <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C223" t="s">
         <v>455</v>
       </c>
       <c r="D223">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
@@ -6631,13 +6655,13 @@
         <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C224" t="s">
         <v>457</v>
       </c>
       <c r="D224">
-        <v>0.56</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
@@ -6645,13 +6669,13 @@
         <v>458</v>
       </c>
       <c r="B225" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C225" t="s">
         <v>459</v>
       </c>
       <c r="D225">
-        <v>0.95</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
@@ -6659,13 +6683,13 @@
         <v>460</v>
       </c>
       <c r="B226" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C226" t="s">
         <v>461</v>
       </c>
       <c r="D226">
-        <v>0.79</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
@@ -6673,13 +6697,13 @@
         <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C227" t="s">
         <v>463</v>
       </c>
       <c r="D227">
-        <v>0.47</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
@@ -6687,13 +6711,13 @@
         <v>464</v>
       </c>
       <c r="B228" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C228" t="s">
         <v>465</v>
       </c>
       <c r="D228">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
@@ -6701,13 +6725,13 @@
         <v>466</v>
       </c>
       <c r="B229" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C229" t="s">
         <v>467</v>
       </c>
       <c r="D229">
-        <v>0.77</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
@@ -6715,13 +6739,13 @@
         <v>468</v>
       </c>
       <c r="B230" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C230" t="s">
         <v>469</v>
       </c>
       <c r="D230">
-        <v>0.91</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
@@ -6729,13 +6753,13 @@
         <v>470</v>
       </c>
       <c r="B231" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C231" t="s">
         <v>471</v>
       </c>
       <c r="D231">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
@@ -6743,13 +6767,13 @@
         <v>472</v>
       </c>
       <c r="B232" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C232" t="s">
         <v>473</v>
       </c>
       <c r="D232">
-        <v>0.38</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
@@ -6757,13 +6781,13 @@
         <v>474</v>
       </c>
       <c r="B233" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C233" t="s">
         <v>475</v>
       </c>
       <c r="D233">
-        <v>0.46</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,13 +6795,13 @@
         <v>476</v>
       </c>
       <c r="B234" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C234" t="s">
         <v>477</v>
       </c>
       <c r="D234">
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
@@ -6785,13 +6809,13 @@
         <v>478</v>
       </c>
       <c r="B235" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C235" t="s">
         <v>479</v>
       </c>
       <c r="D235">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
@@ -6799,13 +6823,13 @@
         <v>480</v>
       </c>
       <c r="B236" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C236" t="s">
         <v>481</v>
       </c>
       <c r="D236">
-        <v>0.86</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
@@ -6813,13 +6837,13 @@
         <v>482</v>
       </c>
       <c r="B237" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C237" t="s">
         <v>483</v>
       </c>
       <c r="D237">
-        <v>0.81</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -6827,13 +6851,13 @@
         <v>484</v>
       </c>
       <c r="B238" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C238" t="s">
         <v>485</v>
       </c>
       <c r="D238">
-        <v>0.94</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
@@ -6841,13 +6865,13 @@
         <v>486</v>
       </c>
       <c r="B239" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C239" t="s">
         <v>487</v>
       </c>
       <c r="D239">
-        <v>0.97</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
@@ -6855,41 +6879,41 @@
         <v>488</v>
       </c>
       <c r="B240" t="s">
+        <v>412</v>
+      </c>
+      <c r="C240" t="s">
         <v>489</v>
       </c>
-      <c r="C240" t="s">
-        <v>490</v>
-      </c>
       <c r="D240">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>490</v>
+      </c>
+      <c r="B241" t="s">
+        <v>412</v>
+      </c>
+      <c r="C241" t="s">
         <v>491</v>
       </c>
-      <c r="B241" t="s">
-        <v>489</v>
-      </c>
-      <c r="C241" t="s">
-        <v>492</v>
-      </c>
       <c r="D241">
-        <v>0.79</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>492</v>
+      </c>
+      <c r="B242" t="s">
         <v>493</v>
-      </c>
-      <c r="B242" t="s">
-        <v>489</v>
       </c>
       <c r="C242" t="s">
         <v>494</v>
       </c>
       <c r="D242">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
@@ -6897,13 +6921,13 @@
         <v>495</v>
       </c>
       <c r="B243" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C243" t="s">
         <v>496</v>
       </c>
       <c r="D243">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
@@ -6911,13 +6935,13 @@
         <v>497</v>
       </c>
       <c r="B244" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C244" t="s">
         <v>498</v>
       </c>
       <c r="D244">
-        <v>0.78</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
@@ -6925,13 +6949,13 @@
         <v>499</v>
       </c>
       <c r="B245" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C245" t="s">
         <v>500</v>
       </c>
       <c r="D245">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
@@ -6939,13 +6963,13 @@
         <v>501</v>
       </c>
       <c r="B246" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C246" t="s">
         <v>502</v>
       </c>
       <c r="D246">
-        <v>0.48</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
@@ -6953,7 +6977,7 @@
         <v>503</v>
       </c>
       <c r="B247" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C247" t="s">
         <v>504</v>
@@ -6967,13 +6991,13 @@
         <v>505</v>
       </c>
       <c r="B248" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C248" t="s">
         <v>506</v>
       </c>
       <c r="D248">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
@@ -6981,13 +7005,13 @@
         <v>507</v>
       </c>
       <c r="B249" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C249" t="s">
         <v>508</v>
       </c>
       <c r="D249">
-        <v>0.87</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
@@ -6995,13 +7019,13 @@
         <v>509</v>
       </c>
       <c r="B250" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C250" t="s">
         <v>510</v>
       </c>
       <c r="D250">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
@@ -7009,13 +7033,13 @@
         <v>511</v>
       </c>
       <c r="B251" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C251" t="s">
         <v>512</v>
       </c>
       <c r="D251">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
@@ -7023,13 +7047,13 @@
         <v>513</v>
       </c>
       <c r="B252" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C252" t="s">
         <v>514</v>
       </c>
       <c r="D252">
-        <v>0.79</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
@@ -7037,13 +7061,13 @@
         <v>515</v>
       </c>
       <c r="B253" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C253" t="s">
         <v>516</v>
       </c>
       <c r="D253">
-        <v>0.67</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
@@ -7051,13 +7075,13 @@
         <v>517</v>
       </c>
       <c r="B254" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C254" t="s">
         <v>518</v>
       </c>
       <c r="D254">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
@@ -7065,13 +7089,13 @@
         <v>519</v>
       </c>
       <c r="B255" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C255" t="s">
         <v>520</v>
       </c>
       <c r="D255">
-        <v>0.69</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
@@ -7079,13 +7103,13 @@
         <v>521</v>
       </c>
       <c r="B256" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C256" t="s">
         <v>522</v>
       </c>
       <c r="D256">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
@@ -7093,13 +7117,13 @@
         <v>523</v>
       </c>
       <c r="B257" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C257" t="s">
         <v>524</v>
       </c>
       <c r="D257">
-        <v>0.79</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
@@ -7107,13 +7131,13 @@
         <v>525</v>
       </c>
       <c r="B258" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C258" t="s">
         <v>526</v>
       </c>
       <c r="D258">
-        <v>0.23</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
@@ -7121,13 +7145,13 @@
         <v>527</v>
       </c>
       <c r="B259" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C259" t="s">
         <v>528</v>
       </c>
       <c r="D259">
-        <v>0.69</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
@@ -7135,41 +7159,41 @@
         <v>529</v>
       </c>
       <c r="B260" t="s">
+        <v>493</v>
+      </c>
+      <c r="C260" t="s">
         <v>530</v>
       </c>
-      <c r="C260" t="s">
-        <v>531</v>
-      </c>
       <c r="D260">
-        <v>0.45</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
+        <v>531</v>
+      </c>
+      <c r="B261" t="s">
+        <v>493</v>
+      </c>
+      <c r="C261" t="s">
         <v>532</v>
       </c>
-      <c r="B261" t="s">
-        <v>530</v>
-      </c>
-      <c r="C261" t="s">
-        <v>533</v>
-      </c>
       <c r="D261">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>533</v>
+      </c>
+      <c r="B262" t="s">
         <v>534</v>
-      </c>
-      <c r="B262" t="s">
-        <v>530</v>
       </c>
       <c r="C262" t="s">
         <v>535</v>
       </c>
       <c r="D262">
-        <v>0.2</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
@@ -7177,13 +7201,13 @@
         <v>536</v>
       </c>
       <c r="B263" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C263" t="s">
         <v>537</v>
       </c>
       <c r="D263">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
@@ -7191,13 +7215,13 @@
         <v>538</v>
       </c>
       <c r="B264" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C264" t="s">
         <v>539</v>
       </c>
       <c r="D264">
-        <v>0.85</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
@@ -7205,13 +7229,13 @@
         <v>540</v>
       </c>
       <c r="B265" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C265" t="s">
         <v>541</v>
       </c>
       <c r="D265">
-        <v>0.79</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
@@ -7219,13 +7243,13 @@
         <v>542</v>
       </c>
       <c r="B266" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C266" t="s">
         <v>543</v>
       </c>
       <c r="D266">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
@@ -7233,13 +7257,13 @@
         <v>544</v>
       </c>
       <c r="B267" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C267" t="s">
         <v>545</v>
       </c>
       <c r="D267">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
@@ -7247,13 +7271,13 @@
         <v>546</v>
       </c>
       <c r="B268" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C268" t="s">
         <v>547</v>
       </c>
       <c r="D268">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
@@ -7261,13 +7285,13 @@
         <v>548</v>
       </c>
       <c r="B269" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C269" t="s">
         <v>549</v>
       </c>
       <c r="D269">
-        <v>0.88</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
@@ -7275,13 +7299,13 @@
         <v>550</v>
       </c>
       <c r="B270" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C270" t="s">
         <v>551</v>
       </c>
       <c r="D270">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
@@ -7289,13 +7313,13 @@
         <v>552</v>
       </c>
       <c r="B271" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C271" t="s">
         <v>553</v>
       </c>
       <c r="D271">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
@@ -7303,13 +7327,13 @@
         <v>554</v>
       </c>
       <c r="B272" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C272" t="s">
         <v>555</v>
       </c>
       <c r="D272">
-        <v>0.74</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
@@ -7317,13 +7341,13 @@
         <v>556</v>
       </c>
       <c r="B273" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C273" t="s">
         <v>557</v>
       </c>
       <c r="D273">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
@@ -7331,13 +7355,13 @@
         <v>558</v>
       </c>
       <c r="B274" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C274" t="s">
         <v>559</v>
       </c>
       <c r="D274">
-        <v>0.84</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
@@ -7345,13 +7369,13 @@
         <v>560</v>
       </c>
       <c r="B275" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C275" t="s">
         <v>561</v>
       </c>
       <c r="D275">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
@@ -7359,13 +7383,13 @@
         <v>562</v>
       </c>
       <c r="B276" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C276" t="s">
         <v>563</v>
       </c>
       <c r="D276">
-        <v>0.91</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
@@ -7373,13 +7397,13 @@
         <v>564</v>
       </c>
       <c r="B277" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C277" t="s">
         <v>565</v>
       </c>
       <c r="D277">
-        <v>0.82</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
@@ -7387,13 +7411,13 @@
         <v>566</v>
       </c>
       <c r="B278" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C278" t="s">
         <v>567</v>
       </c>
       <c r="D278">
-        <v>0.47</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
@@ -7401,13 +7425,13 @@
         <v>568</v>
       </c>
       <c r="B279" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C279" t="s">
         <v>569</v>
       </c>
       <c r="D279">
-        <v>0.61</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
@@ -7415,41 +7439,41 @@
         <v>570</v>
       </c>
       <c r="B280" t="s">
+        <v>534</v>
+      </c>
+      <c r="C280" t="s">
         <v>571</v>
       </c>
-      <c r="C280" t="s">
-        <v>572</v>
-      </c>
       <c r="D280">
-        <v>0.87</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>572</v>
+      </c>
+      <c r="B281" t="s">
+        <v>534</v>
+      </c>
+      <c r="C281" t="s">
         <v>573</v>
       </c>
-      <c r="B281" t="s">
-        <v>571</v>
-      </c>
-      <c r="C281" t="s">
-        <v>574</v>
-      </c>
       <c r="D281">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
+        <v>574</v>
+      </c>
+      <c r="B282" t="s">
         <v>575</v>
-      </c>
-      <c r="B282" t="s">
-        <v>571</v>
       </c>
       <c r="C282" t="s">
         <v>576</v>
       </c>
       <c r="D282">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
@@ -7457,13 +7481,13 @@
         <v>577</v>
       </c>
       <c r="B283" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C283" t="s">
         <v>578</v>
       </c>
       <c r="D283">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
@@ -7471,13 +7495,13 @@
         <v>579</v>
       </c>
       <c r="B284" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C284" t="s">
         <v>580</v>
       </c>
       <c r="D284">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
@@ -7485,13 +7509,13 @@
         <v>581</v>
       </c>
       <c r="B285" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C285" t="s">
         <v>582</v>
       </c>
       <c r="D285">
-        <v>0.91</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
@@ -7499,13 +7523,13 @@
         <v>583</v>
       </c>
       <c r="B286" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C286" t="s">
         <v>584</v>
       </c>
       <c r="D286">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
@@ -7513,13 +7537,13 @@
         <v>585</v>
       </c>
       <c r="B287" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C287" t="s">
         <v>586</v>
       </c>
       <c r="D287">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
@@ -7527,13 +7551,13 @@
         <v>587</v>
       </c>
       <c r="B288" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C288" t="s">
         <v>588</v>
       </c>
       <c r="D288">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
@@ -7541,13 +7565,13 @@
         <v>589</v>
       </c>
       <c r="B289" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C289" t="s">
         <v>590</v>
       </c>
       <c r="D289">
-        <v>0.93</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
@@ -7555,13 +7579,13 @@
         <v>591</v>
       </c>
       <c r="B290" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C290" t="s">
         <v>592</v>
       </c>
       <c r="D290">
-        <v>0.87</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
@@ -7569,13 +7593,13 @@
         <v>593</v>
       </c>
       <c r="B291" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C291" t="s">
         <v>594</v>
       </c>
       <c r="D291">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
@@ -7583,13 +7607,13 @@
         <v>595</v>
       </c>
       <c r="B292" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C292" t="s">
         <v>596</v>
       </c>
       <c r="D292">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
@@ -7597,13 +7621,13 @@
         <v>597</v>
       </c>
       <c r="B293" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C293" t="s">
         <v>598</v>
       </c>
       <c r="D293">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
@@ -7611,13 +7635,13 @@
         <v>599</v>
       </c>
       <c r="B294" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C294" t="s">
         <v>600</v>
       </c>
       <c r="D294">
-        <v>0.62</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
@@ -7625,13 +7649,13 @@
         <v>601</v>
       </c>
       <c r="B295" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C295" t="s">
         <v>602</v>
       </c>
       <c r="D295">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
@@ -7639,13 +7663,13 @@
         <v>603</v>
       </c>
       <c r="B296" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C296" t="s">
         <v>604</v>
       </c>
       <c r="D296">
-        <v>0.95</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
@@ -7653,13 +7677,13 @@
         <v>605</v>
       </c>
       <c r="B297" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C297" t="s">
         <v>606</v>
       </c>
       <c r="D297">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
@@ -7667,13 +7691,13 @@
         <v>607</v>
       </c>
       <c r="B298" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C298" t="s">
         <v>608</v>
       </c>
       <c r="D298">
-        <v>0.57</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
@@ -7681,13 +7705,13 @@
         <v>609</v>
       </c>
       <c r="B299" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C299" t="s">
         <v>610</v>
       </c>
       <c r="D299">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
@@ -7695,13 +7719,13 @@
         <v>611</v>
       </c>
       <c r="B300" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C300" t="s">
         <v>612</v>
       </c>
       <c r="D300">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
@@ -7709,13 +7733,13 @@
         <v>613</v>
       </c>
       <c r="B301" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C301" t="s">
         <v>614</v>
       </c>
       <c r="D301">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
@@ -7723,13 +7747,13 @@
         <v>615</v>
       </c>
       <c r="B302" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C302" t="s">
         <v>616</v>
       </c>
       <c r="D302">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
@@ -7737,13 +7761,13 @@
         <v>617</v>
       </c>
       <c r="B303" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C303" t="s">
         <v>618</v>
       </c>
       <c r="D303">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
@@ -7751,13 +7775,13 @@
         <v>619</v>
       </c>
       <c r="B304" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C304" t="s">
         <v>620</v>
       </c>
       <c r="D304">
-        <v>0.63</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
@@ -7765,13 +7789,13 @@
         <v>621</v>
       </c>
       <c r="B305" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C305" t="s">
         <v>622</v>
       </c>
       <c r="D305">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
@@ -7779,13 +7803,13 @@
         <v>623</v>
       </c>
       <c r="B306" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C306" t="s">
         <v>624</v>
       </c>
       <c r="D306">
-        <v>0.97</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
@@ -7793,13 +7817,13 @@
         <v>625</v>
       </c>
       <c r="B307" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C307" t="s">
         <v>626</v>
       </c>
       <c r="D307">
-        <v>0.63</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
@@ -7807,13 +7831,13 @@
         <v>627</v>
       </c>
       <c r="B308" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C308" t="s">
         <v>628</v>
       </c>
       <c r="D308">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
@@ -7821,13 +7845,13 @@
         <v>629</v>
       </c>
       <c r="B309" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C309" t="s">
         <v>630</v>
       </c>
       <c r="D309">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
@@ -7835,13 +7859,13 @@
         <v>631</v>
       </c>
       <c r="B310" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C310" t="s">
         <v>632</v>
       </c>
       <c r="D310">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
@@ -7849,13 +7873,13 @@
         <v>633</v>
       </c>
       <c r="B311" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C311" t="s">
         <v>634</v>
       </c>
       <c r="D311">
-        <v>0.75</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
@@ -7863,13 +7887,13 @@
         <v>635</v>
       </c>
       <c r="B312" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C312" t="s">
         <v>636</v>
       </c>
       <c r="D312">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
@@ -7877,13 +7901,13 @@
         <v>637</v>
       </c>
       <c r="B313" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C313" t="s">
         <v>638</v>
       </c>
       <c r="D313">
-        <v>0.93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
@@ -7891,13 +7915,13 @@
         <v>639</v>
       </c>
       <c r="B314" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C314" t="s">
         <v>640</v>
       </c>
       <c r="D314">
-        <v>0.83</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
@@ -7905,13 +7929,13 @@
         <v>641</v>
       </c>
       <c r="B315" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C315" t="s">
         <v>642</v>
       </c>
       <c r="D315">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
@@ -7919,13 +7943,13 @@
         <v>643</v>
       </c>
       <c r="B316" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C316" t="s">
         <v>644</v>
       </c>
       <c r="D316">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
@@ -7933,13 +7957,13 @@
         <v>645</v>
       </c>
       <c r="B317" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C317" t="s">
         <v>646</v>
       </c>
       <c r="D317">
-        <v>0.67</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
@@ -7947,13 +7971,13 @@
         <v>647</v>
       </c>
       <c r="B318" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C318" t="s">
         <v>648</v>
       </c>
       <c r="D318">
-        <v>0.48</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
@@ -7961,13 +7985,13 @@
         <v>649</v>
       </c>
       <c r="B319" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C319" t="s">
         <v>650</v>
       </c>
       <c r="D319">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
@@ -7975,41 +7999,41 @@
         <v>651</v>
       </c>
       <c r="B320" t="s">
+        <v>575</v>
+      </c>
+      <c r="C320" t="s">
         <v>652</v>
       </c>
-      <c r="C320" t="s">
-        <v>653</v>
-      </c>
       <c r="D320">
-        <v>0.43</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
+        <v>653</v>
+      </c>
+      <c r="B321" t="s">
+        <v>575</v>
+      </c>
+      <c r="C321" t="s">
         <v>654</v>
       </c>
-      <c r="B321" t="s">
-        <v>652</v>
-      </c>
-      <c r="C321" t="s">
-        <v>655</v>
-      </c>
       <c r="D321">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>655</v>
+      </c>
+      <c r="B322" t="s">
         <v>656</v>
-      </c>
-      <c r="B322" t="s">
-        <v>652</v>
       </c>
       <c r="C322" t="s">
         <v>657</v>
       </c>
       <c r="D322">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
@@ -8017,13 +8041,13 @@
         <v>658</v>
       </c>
       <c r="B323" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C323" t="s">
         <v>659</v>
       </c>
       <c r="D323">
-        <v>0.69</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
@@ -8031,13 +8055,13 @@
         <v>660</v>
       </c>
       <c r="B324" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C324" t="s">
         <v>661</v>
       </c>
       <c r="D324">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
@@ -8045,13 +8069,13 @@
         <v>662</v>
       </c>
       <c r="B325" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C325" t="s">
         <v>663</v>
       </c>
       <c r="D325">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
@@ -8059,13 +8083,13 @@
         <v>664</v>
       </c>
       <c r="B326" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C326" t="s">
         <v>665</v>
       </c>
       <c r="D326">
-        <v>0.71</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
@@ -8073,13 +8097,13 @@
         <v>666</v>
       </c>
       <c r="B327" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C327" t="s">
         <v>667</v>
       </c>
       <c r="D327">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
@@ -8087,13 +8111,13 @@
         <v>668</v>
       </c>
       <c r="B328" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C328" t="s">
         <v>669</v>
       </c>
       <c r="D328">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
@@ -8101,13 +8125,13 @@
         <v>670</v>
       </c>
       <c r="B329" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C329" t="s">
         <v>671</v>
       </c>
       <c r="D329">
-        <v>0.74</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
@@ -8115,13 +8139,13 @@
         <v>672</v>
       </c>
       <c r="B330" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C330" t="s">
         <v>673</v>
       </c>
       <c r="D330">
-        <v>0.91</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
@@ -8129,13 +8153,13 @@
         <v>674</v>
       </c>
       <c r="B331" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C331" t="s">
         <v>675</v>
       </c>
       <c r="D331">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
@@ -8143,13 +8167,13 @@
         <v>676</v>
       </c>
       <c r="B332" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C332" t="s">
         <v>677</v>
       </c>
       <c r="D332">
-        <v>0.62</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
@@ -8157,13 +8181,13 @@
         <v>678</v>
       </c>
       <c r="B333" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C333" t="s">
         <v>679</v>
       </c>
       <c r="D333">
-        <v>0.51</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
@@ -8171,13 +8195,13 @@
         <v>680</v>
       </c>
       <c r="B334" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C334" t="s">
         <v>681</v>
       </c>
       <c r="D334">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
@@ -8185,13 +8209,13 @@
         <v>682</v>
       </c>
       <c r="B335" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C335" t="s">
         <v>683</v>
       </c>
       <c r="D335">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
@@ -8199,13 +8223,13 @@
         <v>684</v>
       </c>
       <c r="B336" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C336" t="s">
         <v>685</v>
       </c>
       <c r="D336">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
@@ -8213,13 +8237,13 @@
         <v>686</v>
       </c>
       <c r="B337" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C337" t="s">
         <v>687</v>
       </c>
       <c r="D337">
-        <v>0.79</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
@@ -8227,13 +8251,13 @@
         <v>688</v>
       </c>
       <c r="B338" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C338" t="s">
         <v>689</v>
       </c>
       <c r="D338">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
@@ -8241,13 +8265,13 @@
         <v>690</v>
       </c>
       <c r="B339" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C339" t="s">
         <v>691</v>
       </c>
       <c r="D339">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
@@ -8255,41 +8279,41 @@
         <v>692</v>
       </c>
       <c r="B340" t="s">
+        <v>656</v>
+      </c>
+      <c r="C340" t="s">
         <v>693</v>
       </c>
-      <c r="C340" t="s">
-        <v>694</v>
-      </c>
       <c r="D340">
-        <v>0.99</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
+        <v>694</v>
+      </c>
+      <c r="B341" t="s">
+        <v>656</v>
+      </c>
+      <c r="C341" t="s">
         <v>695</v>
       </c>
-      <c r="B341" t="s">
-        <v>693</v>
-      </c>
-      <c r="C341" t="s">
-        <v>696</v>
-      </c>
       <c r="D341">
-        <v>0.25</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
+        <v>696</v>
+      </c>
+      <c r="B342" t="s">
         <v>697</v>
-      </c>
-      <c r="B342" t="s">
-        <v>693</v>
       </c>
       <c r="C342" t="s">
         <v>698</v>
       </c>
       <c r="D342">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
@@ -8297,13 +8321,13 @@
         <v>699</v>
       </c>
       <c r="B343" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C343" t="s">
         <v>700</v>
       </c>
       <c r="D343">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
@@ -8311,13 +8335,13 @@
         <v>701</v>
       </c>
       <c r="B344" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C344" t="s">
         <v>702</v>
       </c>
       <c r="D344">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
@@ -8325,13 +8349,13 @@
         <v>703</v>
       </c>
       <c r="B345" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C345" t="s">
         <v>704</v>
       </c>
       <c r="D345">
-        <v>0.79</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
@@ -8339,13 +8363,13 @@
         <v>705</v>
       </c>
       <c r="B346" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C346" t="s">
         <v>706</v>
       </c>
       <c r="D346">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
@@ -8353,13 +8377,13 @@
         <v>707</v>
       </c>
       <c r="B347" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C347" t="s">
         <v>708</v>
       </c>
       <c r="D347">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
@@ -8367,13 +8391,13 @@
         <v>709</v>
       </c>
       <c r="B348" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C348" t="s">
         <v>710</v>
       </c>
       <c r="D348">
-        <v>0.94</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
@@ -8381,13 +8405,13 @@
         <v>711</v>
       </c>
       <c r="B349" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C349" t="s">
         <v>712</v>
       </c>
       <c r="D349">
-        <v>0.81</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
@@ -8395,13 +8419,13 @@
         <v>713</v>
       </c>
       <c r="B350" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C350" t="s">
         <v>714</v>
       </c>
       <c r="D350">
-        <v>0.59</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
@@ -8409,13 +8433,13 @@
         <v>715</v>
       </c>
       <c r="B351" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C351" t="s">
         <v>716</v>
       </c>
       <c r="D351">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
@@ -8423,13 +8447,13 @@
         <v>717</v>
       </c>
       <c r="B352" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C352" t="s">
         <v>718</v>
       </c>
       <c r="D352">
-        <v>0.72</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -8437,13 +8461,13 @@
         <v>719</v>
       </c>
       <c r="B353" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C353" t="s">
         <v>720</v>
       </c>
       <c r="D353">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.25">
@@ -8451,13 +8475,13 @@
         <v>721</v>
       </c>
       <c r="B354" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C354" t="s">
         <v>722</v>
       </c>
       <c r="D354">
-        <v>0.59</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
@@ -8465,13 +8489,13 @@
         <v>723</v>
       </c>
       <c r="B355" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C355" t="s">
         <v>724</v>
       </c>
       <c r="D355">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
@@ -8479,13 +8503,13 @@
         <v>725</v>
       </c>
       <c r="B356" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C356" t="s">
         <v>726</v>
       </c>
       <c r="D356">
-        <v>0.41</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -8493,13 +8517,13 @@
         <v>727</v>
       </c>
       <c r="B357" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C357" t="s">
         <v>728</v>
       </c>
       <c r="D357">
-        <v>0.9</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.25">
@@ -8507,13 +8531,13 @@
         <v>729</v>
       </c>
       <c r="B358" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C358" t="s">
         <v>730</v>
       </c>
       <c r="D358">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.25">
@@ -8521,13 +8545,13 @@
         <v>731</v>
       </c>
       <c r="B359" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C359" t="s">
         <v>732</v>
       </c>
       <c r="D359">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.25">
@@ -8535,41 +8559,41 @@
         <v>733</v>
       </c>
       <c r="B360" t="s">
+        <v>697</v>
+      </c>
+      <c r="C360" t="s">
         <v>734</v>
       </c>
-      <c r="C360" t="s">
-        <v>735</v>
-      </c>
       <c r="D360">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>735</v>
+      </c>
+      <c r="B361" t="s">
+        <v>697</v>
+      </c>
+      <c r="C361" t="s">
         <v>736</v>
       </c>
-      <c r="B361" t="s">
-        <v>734</v>
-      </c>
-      <c r="C361" t="s">
-        <v>737</v>
-      </c>
       <c r="D361">
-        <v>0.67</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>737</v>
+      </c>
+      <c r="B362" t="s">
         <v>738</v>
-      </c>
-      <c r="B362" t="s">
-        <v>734</v>
       </c>
       <c r="C362" t="s">
         <v>739</v>
       </c>
       <c r="D362">
-        <v>0.56</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.25">
@@ -8577,13 +8601,13 @@
         <v>740</v>
       </c>
       <c r="B363" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C363" t="s">
         <v>741</v>
       </c>
       <c r="D363">
-        <v>0.53</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.25">
@@ -8591,13 +8615,13 @@
         <v>742</v>
       </c>
       <c r="B364" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C364" t="s">
         <v>743</v>
       </c>
       <c r="D364">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.25">
@@ -8605,13 +8629,13 @@
         <v>744</v>
       </c>
       <c r="B365" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C365" t="s">
         <v>745</v>
       </c>
       <c r="D365">
-        <v>0.89</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.25">
@@ -8619,13 +8643,13 @@
         <v>746</v>
       </c>
       <c r="B366" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C366" t="s">
         <v>747</v>
       </c>
       <c r="D366">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.25">
@@ -8633,13 +8657,13 @@
         <v>748</v>
       </c>
       <c r="B367" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C367" t="s">
         <v>749</v>
       </c>
       <c r="D367">
-        <v>0.92</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.25">
@@ -8647,13 +8671,13 @@
         <v>750</v>
       </c>
       <c r="B368" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C368" t="s">
         <v>751</v>
       </c>
       <c r="D368">
-        <v>0.62</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
@@ -8661,13 +8685,13 @@
         <v>752</v>
       </c>
       <c r="B369" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C369" t="s">
         <v>753</v>
       </c>
       <c r="D369">
-        <v>0.54</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
@@ -8675,13 +8699,13 @@
         <v>754</v>
       </c>
       <c r="B370" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C370" t="s">
         <v>755</v>
       </c>
       <c r="D370">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
@@ -8689,13 +8713,13 @@
         <v>756</v>
       </c>
       <c r="B371" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C371" t="s">
         <v>757</v>
       </c>
       <c r="D371">
-        <v>0.99</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
@@ -8703,13 +8727,13 @@
         <v>758</v>
       </c>
       <c r="B372" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C372" t="s">
         <v>759</v>
       </c>
       <c r="D372">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
@@ -8717,13 +8741,13 @@
         <v>760</v>
       </c>
       <c r="B373" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C373" t="s">
         <v>761</v>
       </c>
       <c r="D373">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
@@ -8731,13 +8755,13 @@
         <v>762</v>
       </c>
       <c r="B374" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C374" t="s">
         <v>763</v>
       </c>
       <c r="D374">
-        <v>0.85</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
@@ -8745,13 +8769,13 @@
         <v>764</v>
       </c>
       <c r="B375" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C375" t="s">
         <v>765</v>
       </c>
       <c r="D375">
-        <v>0.2</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
@@ -8759,13 +8783,13 @@
         <v>766</v>
       </c>
       <c r="B376" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C376" t="s">
         <v>767</v>
       </c>
       <c r="D376">
-        <v>0.46</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
@@ -8773,13 +8797,13 @@
         <v>768</v>
       </c>
       <c r="B377" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C377" t="s">
         <v>769</v>
       </c>
       <c r="D377">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
@@ -8787,13 +8811,13 @@
         <v>770</v>
       </c>
       <c r="B378" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="C378" t="s">
         <v>771</v>
       </c>
       <c r="D378">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
@@ -8801,55 +8825,55 @@
         <v>772</v>
       </c>
       <c r="B379" t="s">
+        <v>738</v>
+      </c>
+      <c r="C379" t="s">
         <v>773</v>
       </c>
-      <c r="C379" t="s">
-        <v>774</v>
-      </c>
       <c r="D379">
-        <v>0.46</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>774</v>
+      </c>
+      <c r="B380" t="s">
+        <v>738</v>
+      </c>
+      <c r="C380" t="s">
         <v>775</v>
       </c>
-      <c r="B380" t="s">
-        <v>773</v>
-      </c>
-      <c r="C380" t="s">
-        <v>776</v>
-      </c>
       <c r="D380">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>776</v>
+      </c>
+      <c r="B381" t="s">
+        <v>738</v>
+      </c>
+      <c r="C381" t="s">
         <v>777</v>
       </c>
-      <c r="B381" t="s">
-        <v>773</v>
-      </c>
-      <c r="C381" t="s">
-        <v>778</v>
-      </c>
       <c r="D381">
-        <v>0.43</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>778</v>
+      </c>
+      <c r="B382" t="s">
         <v>779</v>
-      </c>
-      <c r="B382" t="s">
-        <v>773</v>
       </c>
       <c r="C382" t="s">
         <v>780</v>
       </c>
       <c r="D382">
-        <v>0.99</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
@@ -8857,13 +8881,13 @@
         <v>781</v>
       </c>
       <c r="B383" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C383" t="s">
         <v>782</v>
       </c>
       <c r="D383">
-        <v>0.64</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
@@ -8871,13 +8895,13 @@
         <v>783</v>
       </c>
       <c r="B384" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C384" t="s">
         <v>784</v>
       </c>
       <c r="D384">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
@@ -8885,13 +8909,13 @@
         <v>785</v>
       </c>
       <c r="B385" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C385" t="s">
         <v>786</v>
       </c>
       <c r="D385">
-        <v>0.87</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
@@ -8899,13 +8923,13 @@
         <v>787</v>
       </c>
       <c r="B386" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C386" t="s">
         <v>788</v>
       </c>
       <c r="D386">
-        <v>0.93</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
@@ -8913,13 +8937,13 @@
         <v>789</v>
       </c>
       <c r="B387" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C387" t="s">
         <v>790</v>
       </c>
       <c r="D387">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
@@ -8927,13 +8951,13 @@
         <v>791</v>
       </c>
       <c r="B388" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C388" t="s">
         <v>792</v>
       </c>
       <c r="D388">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
@@ -8941,7 +8965,7 @@
         <v>793</v>
       </c>
       <c r="B389" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C389" t="s">
         <v>794</v>
@@ -8955,13 +8979,13 @@
         <v>795</v>
       </c>
       <c r="B390" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C390" t="s">
         <v>796</v>
       </c>
       <c r="D390">
-        <v>0.46</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
@@ -8969,13 +8993,13 @@
         <v>797</v>
       </c>
       <c r="B391" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C391" t="s">
         <v>798</v>
       </c>
       <c r="D391">
-        <v>0.88</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
@@ -8983,13 +9007,13 @@
         <v>799</v>
       </c>
       <c r="B392" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C392" t="s">
         <v>800</v>
       </c>
       <c r="D392">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
@@ -8997,13 +9021,13 @@
         <v>801</v>
       </c>
       <c r="B393" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C393" t="s">
         <v>802</v>
       </c>
       <c r="D393">
-        <v>0.9</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
@@ -9011,13 +9035,13 @@
         <v>803</v>
       </c>
       <c r="B394" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C394" t="s">
         <v>804</v>
       </c>
       <c r="D394">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
@@ -9025,13 +9049,13 @@
         <v>805</v>
       </c>
       <c r="B395" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C395" t="s">
         <v>806</v>
       </c>
       <c r="D395">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
@@ -9039,13 +9063,13 @@
         <v>807</v>
       </c>
       <c r="B396" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C396" t="s">
         <v>808</v>
       </c>
       <c r="D396">
-        <v>0.64</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
@@ -9053,13 +9077,13 @@
         <v>809</v>
       </c>
       <c r="B397" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C397" t="s">
         <v>810</v>
       </c>
       <c r="D397">
-        <v>0.65</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -9067,69 +9091,69 @@
         <v>811</v>
       </c>
       <c r="B398" t="s">
+        <v>779</v>
+      </c>
+      <c r="C398" t="s">
         <v>812</v>
       </c>
-      <c r="C398" t="s">
-        <v>813</v>
-      </c>
       <c r="D398">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
+        <v>813</v>
+      </c>
+      <c r="B399" t="s">
+        <v>779</v>
+      </c>
+      <c r="C399" t="s">
         <v>814</v>
       </c>
-      <c r="B399" t="s">
-        <v>812</v>
-      </c>
-      <c r="C399" t="s">
-        <v>815</v>
-      </c>
       <c r="D399">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
+        <v>815</v>
+      </c>
+      <c r="B400" t="s">
+        <v>779</v>
+      </c>
+      <c r="C400" t="s">
         <v>816</v>
       </c>
-      <c r="B400" t="s">
-        <v>812</v>
-      </c>
-      <c r="C400" t="s">
-        <v>817</v>
-      </c>
       <c r="D400">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
+        <v>817</v>
+      </c>
+      <c r="B401" t="s">
+        <v>779</v>
+      </c>
+      <c r="C401" t="s">
         <v>818</v>
       </c>
-      <c r="B401" t="s">
-        <v>812</v>
-      </c>
-      <c r="C401" t="s">
-        <v>819</v>
-      </c>
       <c r="D401">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
+        <v>819</v>
+      </c>
+      <c r="B402" t="s">
         <v>820</v>
-      </c>
-      <c r="B402" t="s">
-        <v>812</v>
       </c>
       <c r="C402" t="s">
         <v>821</v>
       </c>
       <c r="D402">
-        <v>0.81</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
@@ -9137,13 +9161,13 @@
         <v>822</v>
       </c>
       <c r="B403" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C403" t="s">
         <v>823</v>
       </c>
       <c r="D403">
-        <v>0.78</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
@@ -9151,13 +9175,13 @@
         <v>824</v>
       </c>
       <c r="B404" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C404" t="s">
         <v>825</v>
       </c>
       <c r="D404">
-        <v>0.56</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
@@ -9165,13 +9189,13 @@
         <v>826</v>
       </c>
       <c r="B405" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C405" t="s">
         <v>827</v>
       </c>
       <c r="D405">
-        <v>0.7</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
@@ -9179,13 +9203,13 @@
         <v>828</v>
       </c>
       <c r="B406" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C406" t="s">
         <v>829</v>
       </c>
       <c r="D406">
-        <v>0.96</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
@@ -9193,13 +9217,13 @@
         <v>830</v>
       </c>
       <c r="B407" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="C407" t="s">
         <v>831</v>
       </c>
       <c r="D407">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
@@ -9207,69 +9231,69 @@
         <v>832</v>
       </c>
       <c r="B408" t="s">
+        <v>820</v>
+      </c>
+      <c r="C408" t="s">
         <v>833</v>
       </c>
-      <c r="C408" t="s">
-        <v>834</v>
-      </c>
       <c r="D408">
-        <v>0.87</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
+        <v>834</v>
+      </c>
+      <c r="B409" t="s">
+        <v>820</v>
+      </c>
+      <c r="C409" t="s">
         <v>835</v>
       </c>
-      <c r="B409" t="s">
-        <v>833</v>
-      </c>
-      <c r="C409" t="s">
-        <v>836</v>
-      </c>
       <c r="D409">
-        <v>0.6</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
+        <v>836</v>
+      </c>
+      <c r="B410" t="s">
+        <v>820</v>
+      </c>
+      <c r="C410" t="s">
         <v>837</v>
       </c>
-      <c r="B410" t="s">
-        <v>833</v>
-      </c>
-      <c r="C410" t="s">
-        <v>838</v>
-      </c>
       <c r="D410">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
+        <v>838</v>
+      </c>
+      <c r="B411" t="s">
+        <v>820</v>
+      </c>
+      <c r="C411" t="s">
         <v>839</v>
       </c>
-      <c r="B411" t="s">
-        <v>833</v>
-      </c>
-      <c r="C411" t="s">
-        <v>840</v>
-      </c>
       <c r="D411">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
+        <v>840</v>
+      </c>
+      <c r="B412" t="s">
         <v>841</v>
-      </c>
-      <c r="B412" t="s">
-        <v>833</v>
       </c>
       <c r="C412" t="s">
         <v>842</v>
       </c>
       <c r="D412">
-        <v>0.55</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
@@ -9277,13 +9301,13 @@
         <v>843</v>
       </c>
       <c r="B413" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C413" t="s">
         <v>844</v>
       </c>
       <c r="D413">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
@@ -9291,13 +9315,13 @@
         <v>845</v>
       </c>
       <c r="B414" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C414" t="s">
         <v>846</v>
       </c>
       <c r="D414">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -9305,13 +9329,13 @@
         <v>847</v>
       </c>
       <c r="B415" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C415" t="s">
         <v>848</v>
       </c>
       <c r="D415">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -9319,13 +9343,13 @@
         <v>849</v>
       </c>
       <c r="B416" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C416" t="s">
         <v>850</v>
       </c>
       <c r="D416">
-        <v>0.44</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -9333,13 +9357,13 @@
         <v>851</v>
       </c>
       <c r="B417" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C417" t="s">
         <v>852</v>
       </c>
       <c r="D417">
-        <v>0.78</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
@@ -9347,13 +9371,13 @@
         <v>853</v>
       </c>
       <c r="B418" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C418" t="s">
         <v>854</v>
       </c>
       <c r="D418">
-        <v>0.34</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
@@ -9361,13 +9385,13 @@
         <v>855</v>
       </c>
       <c r="B419" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C419" t="s">
         <v>856</v>
       </c>
       <c r="D419">
-        <v>0.69</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -9375,13 +9399,13 @@
         <v>857</v>
       </c>
       <c r="B420" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C420" t="s">
         <v>858</v>
       </c>
       <c r="D420">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -9389,13 +9413,13 @@
         <v>859</v>
       </c>
       <c r="B421" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C421" t="s">
         <v>860</v>
       </c>
       <c r="D421">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -9403,13 +9427,13 @@
         <v>861</v>
       </c>
       <c r="B422" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C422" t="s">
         <v>862</v>
       </c>
       <c r="D422">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -9417,13 +9441,13 @@
         <v>863</v>
       </c>
       <c r="B423" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C423" t="s">
         <v>864</v>
       </c>
       <c r="D423">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -9431,13 +9455,13 @@
         <v>865</v>
       </c>
       <c r="B424" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C424" t="s">
         <v>866</v>
       </c>
       <c r="D424">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -9445,13 +9469,13 @@
         <v>867</v>
       </c>
       <c r="B425" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C425" t="s">
         <v>868</v>
       </c>
       <c r="D425">
-        <v>0.54</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
@@ -9459,13 +9483,13 @@
         <v>869</v>
       </c>
       <c r="B426" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C426" t="s">
         <v>870</v>
       </c>
       <c r="D426">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -9473,13 +9497,13 @@
         <v>871</v>
       </c>
       <c r="B427" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C427" t="s">
         <v>872</v>
       </c>
       <c r="D427">
-        <v>0.94</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
@@ -9487,69 +9511,69 @@
         <v>873</v>
       </c>
       <c r="B428" t="s">
+        <v>841</v>
+      </c>
+      <c r="C428" t="s">
         <v>874</v>
       </c>
-      <c r="C428" t="s">
-        <v>875</v>
-      </c>
       <c r="D428">
-        <v>0.73</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
+        <v>875</v>
+      </c>
+      <c r="B429" t="s">
+        <v>841</v>
+      </c>
+      <c r="C429" t="s">
         <v>876</v>
       </c>
-      <c r="B429" t="s">
-        <v>874</v>
-      </c>
-      <c r="C429" t="s">
-        <v>877</v>
-      </c>
       <c r="D429">
-        <v>0.34</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
+        <v>877</v>
+      </c>
+      <c r="B430" t="s">
+        <v>841</v>
+      </c>
+      <c r="C430" t="s">
         <v>878</v>
       </c>
-      <c r="B430" t="s">
-        <v>874</v>
-      </c>
-      <c r="C430" t="s">
-        <v>879</v>
-      </c>
       <c r="D430">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
+        <v>879</v>
+      </c>
+      <c r="B431" t="s">
+        <v>841</v>
+      </c>
+      <c r="C431" t="s">
         <v>880</v>
       </c>
-      <c r="B431" t="s">
-        <v>874</v>
-      </c>
-      <c r="C431" t="s">
-        <v>881</v>
-      </c>
       <c r="D431">
-        <v>0.82</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
+        <v>881</v>
+      </c>
+      <c r="B432" t="s">
         <v>882</v>
-      </c>
-      <c r="B432" t="s">
-        <v>874</v>
       </c>
       <c r="C432" t="s">
         <v>883</v>
       </c>
       <c r="D432">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
@@ -9557,13 +9581,13 @@
         <v>884</v>
       </c>
       <c r="B433" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="C433" t="s">
         <v>885</v>
       </c>
       <c r="D433">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
@@ -9571,13 +9595,13 @@
         <v>886</v>
       </c>
       <c r="B434" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="C434" t="s">
         <v>887</v>
       </c>
       <c r="D434">
-        <v>0.62</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
@@ -9585,13 +9609,13 @@
         <v>888</v>
       </c>
       <c r="B435" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="C435" t="s">
         <v>889</v>
       </c>
       <c r="D435">
-        <v>0.52</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
@@ -9599,7 +9623,7 @@
         <v>890</v>
       </c>
       <c r="B436" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="C436" t="s">
         <v>891</v>
@@ -9613,13 +9637,13 @@
         <v>892</v>
       </c>
       <c r="B437" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="C437" t="s">
         <v>893</v>
       </c>
       <c r="D437">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -9627,69 +9651,69 @@
         <v>894</v>
       </c>
       <c r="B438" t="s">
+        <v>882</v>
+      </c>
+      <c r="C438" t="s">
         <v>895</v>
       </c>
-      <c r="C438" t="s">
-        <v>896</v>
-      </c>
       <c r="D438">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
+        <v>896</v>
+      </c>
+      <c r="B439" t="s">
+        <v>882</v>
+      </c>
+      <c r="C439" t="s">
         <v>897</v>
       </c>
-      <c r="B439" t="s">
-        <v>895</v>
-      </c>
-      <c r="C439" t="s">
-        <v>898</v>
-      </c>
       <c r="D439">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
+        <v>898</v>
+      </c>
+      <c r="B440" t="s">
+        <v>882</v>
+      </c>
+      <c r="C440" t="s">
         <v>899</v>
       </c>
-      <c r="B440" t="s">
-        <v>895</v>
-      </c>
-      <c r="C440" t="s">
-        <v>900</v>
-      </c>
       <c r="D440">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
+        <v>900</v>
+      </c>
+      <c r="B441" t="s">
+        <v>882</v>
+      </c>
+      <c r="C441" t="s">
         <v>901</v>
       </c>
-      <c r="B441" t="s">
-        <v>895</v>
-      </c>
-      <c r="C441" t="s">
-        <v>902</v>
-      </c>
       <c r="D441">
-        <v>0.8</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
+        <v>902</v>
+      </c>
+      <c r="B442" t="s">
         <v>903</v>
-      </c>
-      <c r="B442" t="s">
-        <v>895</v>
       </c>
       <c r="C442" t="s">
         <v>904</v>
       </c>
       <c r="D442">
-        <v>0.89</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.25">
@@ -9697,13 +9721,13 @@
         <v>905</v>
       </c>
       <c r="B443" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C443" t="s">
         <v>906</v>
       </c>
       <c r="D443">
-        <v>0.93</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.25">
@@ -9711,13 +9735,13 @@
         <v>907</v>
       </c>
       <c r="B444" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C444" t="s">
         <v>908</v>
       </c>
       <c r="D444">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.25">
@@ -9725,13 +9749,13 @@
         <v>909</v>
       </c>
       <c r="B445" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C445" t="s">
         <v>910</v>
       </c>
       <c r="D445">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.25">
@@ -9739,13 +9763,13 @@
         <v>911</v>
       </c>
       <c r="B446" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C446" t="s">
         <v>912</v>
       </c>
       <c r="D446">
-        <v>0.81</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
@@ -9753,13 +9777,13 @@
         <v>913</v>
       </c>
       <c r="B447" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C447" t="s">
         <v>914</v>
       </c>
       <c r="D447">
-        <v>0.94</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
@@ -9767,13 +9791,13 @@
         <v>915</v>
       </c>
       <c r="B448" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C448" t="s">
         <v>916</v>
       </c>
       <c r="D448">
-        <v>0.98</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.25">
@@ -9781,13 +9805,13 @@
         <v>917</v>
       </c>
       <c r="B449" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C449" t="s">
         <v>918</v>
       </c>
       <c r="D449">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.25">
@@ -9795,13 +9819,13 @@
         <v>919</v>
       </c>
       <c r="B450" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C450" t="s">
         <v>920</v>
       </c>
       <c r="D450">
-        <v>0.65</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.25">
@@ -9809,13 +9833,13 @@
         <v>921</v>
       </c>
       <c r="B451" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C451" t="s">
         <v>922</v>
       </c>
       <c r="D451">
-        <v>0.57</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.25">
@@ -9823,13 +9847,13 @@
         <v>923</v>
       </c>
       <c r="B452" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C452" t="s">
         <v>924</v>
       </c>
       <c r="D452">
-        <v>0.72</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.25">
@@ -9837,13 +9861,13 @@
         <v>925</v>
       </c>
       <c r="B453" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C453" t="s">
         <v>926</v>
       </c>
       <c r="D453">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.25">
@@ -9851,13 +9875,13 @@
         <v>927</v>
       </c>
       <c r="B454" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C454" t="s">
         <v>928</v>
       </c>
       <c r="D454">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.25">
@@ -9865,13 +9889,13 @@
         <v>929</v>
       </c>
       <c r="B455" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C455" t="s">
         <v>930</v>
       </c>
       <c r="D455">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.25">
@@ -9879,13 +9903,13 @@
         <v>931</v>
       </c>
       <c r="B456" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C456" t="s">
         <v>932</v>
       </c>
       <c r="D456">
-        <v>0.82</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.25">
@@ -9893,13 +9917,13 @@
         <v>933</v>
       </c>
       <c r="B457" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C457" t="s">
         <v>934</v>
       </c>
       <c r="D457">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.25">
@@ -9907,69 +9931,69 @@
         <v>935</v>
       </c>
       <c r="B458" t="s">
+        <v>903</v>
+      </c>
+      <c r="C458" t="s">
         <v>936</v>
       </c>
-      <c r="C458" t="s">
-        <v>937</v>
-      </c>
       <c r="D458">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
+        <v>937</v>
+      </c>
+      <c r="B459" t="s">
+        <v>903</v>
+      </c>
+      <c r="C459" t="s">
         <v>938</v>
       </c>
-      <c r="B459" t="s">
-        <v>936</v>
-      </c>
-      <c r="C459" t="s">
-        <v>939</v>
-      </c>
       <c r="D459">
-        <v>0.61</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
+        <v>939</v>
+      </c>
+      <c r="B460" t="s">
+        <v>903</v>
+      </c>
+      <c r="C460" t="s">
         <v>940</v>
       </c>
-      <c r="B460" t="s">
-        <v>936</v>
-      </c>
-      <c r="C460" t="s">
-        <v>941</v>
-      </c>
       <c r="D460">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
+        <v>941</v>
+      </c>
+      <c r="B461" t="s">
+        <v>903</v>
+      </c>
+      <c r="C461" t="s">
         <v>942</v>
       </c>
-      <c r="B461" t="s">
-        <v>936</v>
-      </c>
-      <c r="C461" t="s">
-        <v>943</v>
-      </c>
       <c r="D461">
-        <v>0.98</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
+        <v>943</v>
+      </c>
+      <c r="B462" t="s">
         <v>944</v>
-      </c>
-      <c r="B462" t="s">
-        <v>936</v>
       </c>
       <c r="C462" t="s">
         <v>945</v>
       </c>
       <c r="D462">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.25">
@@ -9977,13 +10001,13 @@
         <v>946</v>
       </c>
       <c r="B463" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C463" t="s">
         <v>947</v>
       </c>
       <c r="D463">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.25">
@@ -9991,13 +10015,13 @@
         <v>948</v>
       </c>
       <c r="B464" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C464" t="s">
         <v>949</v>
       </c>
       <c r="D464">
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.25">
@@ -10005,13 +10029,13 @@
         <v>950</v>
       </c>
       <c r="B465" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C465" t="s">
         <v>951</v>
       </c>
       <c r="D465">
-        <v>0.65</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.25">
@@ -10019,13 +10043,13 @@
         <v>952</v>
       </c>
       <c r="B466" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C466" t="s">
         <v>953</v>
       </c>
       <c r="D466">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.25">
@@ -10033,13 +10057,13 @@
         <v>954</v>
       </c>
       <c r="B467" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C467" t="s">
         <v>955</v>
       </c>
       <c r="D467">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.25">
@@ -10047,13 +10071,13 @@
         <v>956</v>
       </c>
       <c r="B468" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C468" t="s">
         <v>957</v>
       </c>
       <c r="D468">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.25">
@@ -10061,13 +10085,13 @@
         <v>958</v>
       </c>
       <c r="B469" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C469" t="s">
         <v>959</v>
       </c>
       <c r="D469">
-        <v>0.98</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.25">
@@ -10075,13 +10099,13 @@
         <v>960</v>
       </c>
       <c r="B470" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C470" t="s">
         <v>961</v>
       </c>
       <c r="D470">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.25">
@@ -10089,13 +10113,13 @@
         <v>962</v>
       </c>
       <c r="B471" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C471" t="s">
         <v>963</v>
       </c>
       <c r="D471">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.25">
@@ -10103,13 +10127,13 @@
         <v>964</v>
       </c>
       <c r="B472" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C472" t="s">
         <v>965</v>
       </c>
       <c r="D472">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.25">
@@ -10117,13 +10141,13 @@
         <v>966</v>
       </c>
       <c r="B473" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C473" t="s">
         <v>967</v>
       </c>
       <c r="D473">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.25">
@@ -10131,13 +10155,13 @@
         <v>968</v>
       </c>
       <c r="B474" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C474" t="s">
         <v>969</v>
       </c>
       <c r="D474">
-        <v>0.93</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.25">
@@ -10145,13 +10169,13 @@
         <v>970</v>
       </c>
       <c r="B475" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C475" t="s">
         <v>971</v>
       </c>
       <c r="D475">
-        <v>0.94</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.25">
@@ -10159,13 +10183,13 @@
         <v>972</v>
       </c>
       <c r="B476" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C476" t="s">
         <v>973</v>
       </c>
       <c r="D476">
-        <v>0.75</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.25">
@@ -10173,13 +10197,13 @@
         <v>974</v>
       </c>
       <c r="B477" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C477" t="s">
         <v>975</v>
       </c>
       <c r="D477">
-        <v>0.55</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.25">
@@ -10187,13 +10211,13 @@
         <v>976</v>
       </c>
       <c r="B478" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C478" t="s">
         <v>977</v>
       </c>
       <c r="D478">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.25">
@@ -10201,13 +10225,13 @@
         <v>978</v>
       </c>
       <c r="B479" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C479" t="s">
         <v>979</v>
       </c>
       <c r="D479">
-        <v>0.78</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.25">
@@ -10215,13 +10239,13 @@
         <v>980</v>
       </c>
       <c r="B480" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C480" t="s">
         <v>981</v>
       </c>
       <c r="D480">
-        <v>0.64</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
@@ -10229,7 +10253,7 @@
         <v>982</v>
       </c>
       <c r="B481" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C481" t="s">
         <v>983</v>
@@ -10243,13 +10267,13 @@
         <v>984</v>
       </c>
       <c r="B482" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C482" t="s">
         <v>985</v>
       </c>
       <c r="D482">
-        <v>0.59</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
@@ -10257,13 +10281,13 @@
         <v>986</v>
       </c>
       <c r="B483" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C483" t="s">
         <v>987</v>
       </c>
       <c r="D483">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
@@ -10271,13 +10295,13 @@
         <v>988</v>
       </c>
       <c r="B484" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C484" t="s">
         <v>989</v>
       </c>
       <c r="D484">
-        <v>0.66</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
@@ -10285,13 +10309,13 @@
         <v>990</v>
       </c>
       <c r="B485" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C485" t="s">
         <v>991</v>
       </c>
       <c r="D485">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.25">
@@ -10299,13 +10323,13 @@
         <v>992</v>
       </c>
       <c r="B486" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C486" t="s">
         <v>993</v>
       </c>
       <c r="D486">
-        <v>0.64</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.25">
@@ -10313,13 +10337,13 @@
         <v>994</v>
       </c>
       <c r="B487" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C487" t="s">
         <v>995</v>
       </c>
       <c r="D487">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.25">
@@ -10327,13 +10351,13 @@
         <v>996</v>
       </c>
       <c r="B488" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C488" t="s">
         <v>997</v>
       </c>
       <c r="D488">
-        <v>0.84</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.25">
@@ -10341,7 +10365,7 @@
         <v>998</v>
       </c>
       <c r="B489" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C489" t="s">
         <v>999</v>
@@ -10355,13 +10379,13 @@
         <v>1000</v>
       </c>
       <c r="B490" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C490" t="s">
         <v>1001</v>
       </c>
       <c r="D490">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.25">
@@ -10369,13 +10393,13 @@
         <v>1002</v>
       </c>
       <c r="B491" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C491" t="s">
         <v>1003</v>
       </c>
       <c r="D491">
-        <v>0.43</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.25">
@@ -10383,13 +10407,13 @@
         <v>1004</v>
       </c>
       <c r="B492" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C492" t="s">
         <v>1005</v>
       </c>
       <c r="D492">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
@@ -10397,13 +10421,13 @@
         <v>1006</v>
       </c>
       <c r="B493" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C493" t="s">
         <v>1007</v>
       </c>
       <c r="D493">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
@@ -10411,13 +10435,13 @@
         <v>1008</v>
       </c>
       <c r="B494" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C494" t="s">
         <v>1009</v>
       </c>
       <c r="D494">
-        <v>0.96</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
@@ -10425,13 +10449,13 @@
         <v>1010</v>
       </c>
       <c r="B495" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C495" t="s">
         <v>1011</v>
       </c>
       <c r="D495">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
@@ -10439,13 +10463,13 @@
         <v>1012</v>
       </c>
       <c r="B496" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C496" t="s">
         <v>1013</v>
       </c>
       <c r="D496">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.25">
@@ -10453,13 +10477,13 @@
         <v>1014</v>
       </c>
       <c r="B497" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C497" t="s">
         <v>1015</v>
       </c>
       <c r="D497">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.25">
@@ -10467,13 +10491,13 @@
         <v>1016</v>
       </c>
       <c r="B498" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C498" t="s">
         <v>1017</v>
       </c>
       <c r="D498">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.25">
@@ -10481,13 +10505,13 @@
         <v>1018</v>
       </c>
       <c r="B499" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C499" t="s">
         <v>1019</v>
       </c>
       <c r="D499">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.25">
@@ -10495,13 +10519,13 @@
         <v>1020</v>
       </c>
       <c r="B500" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C500" t="s">
         <v>1021</v>
       </c>
       <c r="D500">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.25">
@@ -10509,13 +10533,13 @@
         <v>1022</v>
       </c>
       <c r="B501" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C501" t="s">
         <v>1023</v>
       </c>
       <c r="D501">
-        <v>0.89</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
@@ -10523,13 +10547,13 @@
         <v>1024</v>
       </c>
       <c r="B502" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C502" t="s">
         <v>1025</v>
       </c>
       <c r="D502">
-        <v>0.72</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
@@ -10537,13 +10561,13 @@
         <v>1026</v>
       </c>
       <c r="B503" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C503" t="s">
         <v>1027</v>
       </c>
       <c r="D503">
-        <v>0.96</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
@@ -10551,13 +10575,13 @@
         <v>1028</v>
       </c>
       <c r="B504" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C504" t="s">
         <v>1029</v>
       </c>
       <c r="D504">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
@@ -10565,13 +10589,13 @@
         <v>1030</v>
       </c>
       <c r="B505" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C505" t="s">
         <v>1031</v>
       </c>
       <c r="D505">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
@@ -10579,13 +10603,13 @@
         <v>1032</v>
       </c>
       <c r="B506" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C506" t="s">
         <v>1033</v>
       </c>
       <c r="D506">
-        <v>0.89</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
@@ -10593,13 +10617,69 @@
         <v>1034</v>
       </c>
       <c r="B507" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C507" t="s">
         <v>1035</v>
       </c>
       <c r="D507">
-        <v>0.2</v>
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B508" t="s">
+        <v>944</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D508">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B509" t="s">
+        <v>944</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D509">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B510" t="s">
+        <v>944</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D510">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B511" t="s">
+        <v>944</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D511">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
